--- a/data/trans_orig/P57B5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido rebosante de energía en 2023</t>
+          <t>Población según se ha sentido rebosante de energía en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226219</t>
+          <t>223015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>292190</t>
+          <t>287866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146239</t>
+          <t>145862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193784</t>
+          <t>193284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385644</t>
+          <t>388321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>469072</t>
+          <t>469979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85563</t>
+          <t>87010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151640</t>
+          <t>152017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76892</t>
+          <t>79649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124245</t>
+          <t>125334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176103</t>
+          <t>178627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257819</t>
+          <t>255195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39139</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>59815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42102</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86910</t>
+          <t>83170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174997</t>
+          <t>176191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228683</t>
+          <t>228835</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>96783</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225569</t>
+          <t>224916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>303375</t>
+          <t>294906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>434441</t>
+          <t>439561</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151838</t>
+          <t>150931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203524</t>
+          <t>201916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206681</t>
+          <t>205820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359947</t>
+          <t>368055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>379267</t>
+          <t>375609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>550377</t>
+          <t>545942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>70928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61170</t>
+          <t>60271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104853</t>
+          <t>105775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241695</t>
+          <t>240946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289895</t>
+          <t>287195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192425</t>
+          <t>192808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231795</t>
+          <t>231238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>447616</t>
+          <t>444889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>510137</t>
+          <t>507711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166384</t>
+          <t>166656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211607</t>
+          <t>211236</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>221776</t>
+          <t>221083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>258750</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>399103</t>
+          <t>402010</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>459809</t>
+          <t>460158</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48609</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>81237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84373</t>
+          <t>85474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117815</t>
+          <t>117291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155047</t>
+          <t>157254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32309</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51159</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>320233</t>
+          <t>320179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>707735</t>
+          <t>718205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166294</t>
+          <t>166778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>216922</t>
+          <t>218906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>505165</t>
+          <t>502919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1075327</t>
+          <t>1044406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>65,41%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119268</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>378548</t>
+          <t>380722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318055</t>
+          <t>320357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>403435</t>
+          <t>403655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>353626</t>
+          <t>372971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>739470</t>
+          <t>739195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>47958</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169003</t>
+          <t>167340</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104248</t>
+          <t>104947</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145166</t>
+          <t>145429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137382</t>
+          <t>133689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>291504</t>
+          <t>292920</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>29672</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58952</t>
+          <t>57665</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>85868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156832</t>
+          <t>154920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>200343</t>
+          <t>197789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117931</t>
+          <t>116667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>149848</t>
+          <t>147655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>286901</t>
+          <t>284725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>336824</t>
+          <t>337023</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219852</t>
+          <t>219382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>264232</t>
+          <t>264639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215305</t>
+          <t>215767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248808</t>
+          <t>249611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>447202</t>
+          <t>448676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>502420</t>
+          <t>504748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>95224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130366</t>
+          <t>130138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129379</t>
+          <t>129015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159172</t>
+          <t>158203</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232262</t>
+          <t>232945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>278214</t>
+          <t>279767</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39109</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48317</t>
+          <t>48903</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54749</t>
+          <t>54437</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>81552</t>
+          <t>80639</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>89307</t>
+          <t>90095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119159</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145246</t>
+          <t>143328</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>101631</t>
+          <t>94965</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>254518</t>
+          <t>254736</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>141350</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>173216</t>
+          <t>171520</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>242151</t>
+          <t>243333</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>507832</t>
+          <t>512752</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>399377</t>
+          <t>398388</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>736304</t>
+          <t>747485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>77314</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>103739</t>
+          <t>102652</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>46102</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>173677</t>
+          <t>172836</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>106672</t>
+          <t>105718</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>262454</t>
+          <t>263921</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21550</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>64510</t>
+          <t>64575</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>45092</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>66258</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54851</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>86884</t>
+          <t>87727</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>114545</t>
+          <t>114657</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>103044</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>129861</t>
+          <t>129766</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>140740</t>
+          <t>139626</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>168049</t>
+          <t>168029</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>250325</t>
+          <t>251484</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>288127</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>67421</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>91374</t>
+          <t>92543</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>130482</t>
+          <t>130253</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>158243</t>
+          <t>158706</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>204909</t>
+          <t>207407</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>241094</t>
+          <t>241958</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>67654</t>
+          <t>67944</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>88699</t>
+          <t>89283</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>93161</t>
+          <t>91824</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>119398</t>
+          <t>119235</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1384710</t>
+          <t>1386095</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2007510</t>
+          <t>2037101</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>842755</t>
+          <t>840669</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1123970</t>
+          <t>1128748</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2586330</t>
+          <t>2586331</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2348496</t>
+          <t>2339581</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3114033</t>
+          <t>3132339</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>963695</t>
+          <t>946436</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1375661</t>
+          <t>1380549</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1547874</t>
+          <t>1542845</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2105454</t>
+          <t>2069430</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2682597</t>
+          <t>2662257</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3351969</t>
+          <t>3330640</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>387416</t>
+          <t>383747</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>571091</t>
+          <t>564978</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>551040</t>
+          <t>567094</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>749648</t>
+          <t>756029</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1042357</t>
+          <t>1044341</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1300598</t>
+          <t>1297988</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>103210</t>
+          <t>101090</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>161817</t>
+          <t>157080</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>185491</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>256074</t>
+          <t>259761</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>312689</t>
+          <t>310195</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>403442</t>
+          <t>400583</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">

--- a/data/trans_orig/P57B5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>260892</t>
+          <t>266139</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>223015</t>
+          <t>235731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>287866</t>
+          <t>295259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>170273</t>
+          <t>196887</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145862</t>
+          <t>168457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193284</t>
+          <t>222205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>431165</t>
+          <t>463026</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>388321</t>
+          <t>421325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>469979</t>
+          <t>501781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>115425</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87010</t>
+          <t>90442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152017</t>
+          <t>147665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>99541</t>
+          <t>113983</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79649</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>140465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>214966</t>
+          <t>230692</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178627</t>
+          <t>195826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255195</t>
+          <t>272140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>59684</t>
+          <t>66713</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41234</t>
+          <t>49166</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83170</t>
+          <t>94474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>201507</t>
+          <t>230127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176191</t>
+          <t>200165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228835</t>
+          <t>260336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>187308</t>
+          <t>206217</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96783</t>
+          <t>182001</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224916</t>
+          <t>229210</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>388815</t>
+          <t>436344</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>294906</t>
+          <t>400815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>439561</t>
+          <t>474472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>176282</t>
+          <t>197534</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150931</t>
+          <t>170668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201916</t>
+          <t>227950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>254732</t>
+          <t>214290</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205820</t>
+          <t>191861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>368055</t>
+          <t>240707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>431014</t>
+          <t>411824</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375609</t>
+          <t>374611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>545942</t>
+          <t>448410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>64224</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>48523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70928</t>
+          <t>80143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>83581</t>
+          <t>97711</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>76643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105775</t>
+          <t>118655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26938</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>25876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>264631</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240946</t>
+          <t>278189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287195</t>
+          <t>331388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>211994</t>
+          <t>238741</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192808</t>
+          <t>217392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231238</t>
+          <t>258169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>476625</t>
+          <t>542900</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>444889</t>
+          <t>508078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>507711</t>
+          <t>576300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>188682</t>
+          <t>225868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166656</t>
+          <t>198962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>211236</t>
+          <t>250081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>241221</t>
+          <t>280009</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>221083</t>
+          <t>259793</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>301718</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>429903</t>
+          <t>505876</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>402010</t>
+          <t>473102</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>460158</t>
+          <t>539038</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>69505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>54163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81237</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>72240</t>
+          <t>83417</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60221</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85474</t>
+          <t>97920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135405</t>
+          <t>152922</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117291</t>
+          <t>131239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157254</t>
+          <t>175753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31457</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26259</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>486268</t>
+          <t>263394</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>320179</t>
+          <t>238743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>718205</t>
+          <t>291101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>196500</t>
+          <t>216506</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166778</t>
+          <t>195309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218906</t>
+          <t>235893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>682769</t>
+          <t>479900</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>502919</t>
+          <t>447025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1044406</t>
+          <t>511953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>265310</t>
+          <t>290932</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119645</t>
+          <t>265309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>380722</t>
+          <t>315982</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>345887</t>
+          <t>339657</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>320357</t>
+          <t>319731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>403655</t>
+          <t>362374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>611197</t>
+          <t>630588</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372971</t>
+          <t>598240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>739195</t>
+          <t>666021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>122476</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>102167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167340</t>
+          <t>143444</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126767</t>
+          <t>138237</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104947</t>
+          <t>122601</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>239976</t>
+          <t>260713</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133689</t>
+          <t>234683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>292920</t>
+          <t>286756</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38731</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39770</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57665</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>62769</t>
+          <t>62208</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38238</t>
+          <t>48349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85868</t>
+          <t>75775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>708924</t>
+          <t>732793</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708924</t>
+          <t>732793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708924</t>
+          <t>732793</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1596711</t>
+          <t>1433410</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1596711</t>
+          <t>1433410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1596711</t>
+          <t>1433410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>178297</t>
+          <t>197853</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>154920</t>
+          <t>176481</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>197789</t>
+          <t>221063</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>132501</t>
+          <t>151107</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116667</t>
+          <t>134898</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>168116</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>310797</t>
+          <t>348960</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>284725</t>
+          <t>321680</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>337023</t>
+          <t>378127</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>241519</t>
+          <t>258170</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219382</t>
+          <t>234309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>264639</t>
+          <t>282384</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>233418</t>
+          <t>259858</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215767</t>
+          <t>241934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249611</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>474937</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>448676</t>
+          <t>486669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>504748</t>
+          <t>546407</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>112675</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95224</t>
+          <t>105234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130138</t>
+          <t>143069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>143559</t>
+          <t>156200</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129015</t>
+          <t>139117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158203</t>
+          <t>171905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>256235</t>
+          <t>278075</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232945</t>
+          <t>253744</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>279767</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>72543</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>54437</t>
+          <t>58930</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>80639</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560691</t>
+          <t>608752</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1108596</t>
+          <t>1217607</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1108596</t>
+          <t>1217607</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1108596</t>
+          <t>1217607</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>103645</t>
+          <t>117130</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>101560</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117612</t>
+          <t>133061</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>92079</t>
+          <t>100437</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>87982</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>113258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>195724</t>
+          <t>217568</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>94965</t>
+          <t>198416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>254736</t>
+          <t>237236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -3683,17 +3683,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>156508</t>
+          <t>173129</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141350</t>
+          <t>157342</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>171520</t>
+          <t>191546</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>370066</t>
+          <t>182027</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>243333</t>
+          <t>166930</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>512752</t>
+          <t>196616</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>526575</t>
+          <t>355157</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>398388</t>
+          <t>330367</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>747485</t>
+          <t>375315</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>91188</t>
+          <t>98021</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>85750</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>102652</t>
+          <t>113595</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>110296</t>
+          <t>119576</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>106021</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>172836</t>
+          <t>133107</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>201484</t>
+          <t>217597</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105718</t>
+          <t>199169</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>263921</t>
+          <t>238242</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>24373</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>32782</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>42926</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>64575</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>365966</t>
+          <t>404784</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>365966</t>
+          <t>404784</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>365966</t>
+          <t>404784</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>605223</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>605223</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>605223</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>971189</t>
+          <t>842951</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>971189</t>
+          <t>842951</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>971189</t>
+          <t>842951</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66258</t>
+          <t>72735</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>50517</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>40445</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>60446</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>100436</t>
+          <t>111276</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>96987</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>114657</t>
+          <t>129194</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>115988</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>129766</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>153802</t>
+          <t>168755</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>139626</t>
+          <t>152704</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>168029</t>
+          <t>184001</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>269790</t>
+          <t>297450</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>251484</t>
+          <t>276243</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>289109</t>
+          <t>320865</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>79241</t>
+          <t>85911</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>67421</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>92543</t>
+          <t>98661</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>155706</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>130253</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>158706</t>
+          <t>172149</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>223117</t>
+          <t>241617</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>207407</t>
+          <t>223372</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>241958</t>
+          <t>261547</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -4478,102 +4478,102 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>84002</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>72421</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>97048</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>114524</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>100083</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>129855</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>14,97%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>13,08%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>77773</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>67944</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>89283</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>105940</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>91824</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>119235</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>278745</t>
+          <t>305887</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>278745</t>
+          <t>305887</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>278745</t>
+          <t>305887</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>420539</t>
+          <t>458981</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>420539</t>
+          <t>458981</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>420539</t>
+          <t>458981</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>699283</t>
+          <t>764867</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>699283</t>
+          <t>764867</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>699283</t>
+          <t>764867</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1550589</t>
+          <t>1439562</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1386095</t>
+          <t>1368687</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2037101</t>
+          <t>1506083</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1035742</t>
+          <t>1160413</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>840669</t>
+          <t>1103036</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1128748</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2586331</t>
+          <t>2599975</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2339581</t>
+          <t>2511928</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3132339</t>
+          <t>2687293</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1259715</t>
+          <t>1391037</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>946436</t>
+          <t>1326609</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1380549</t>
+          <t>1456064</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1698668</t>
+          <t>1558579</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1542845</t>
+          <t>1503497</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2069430</t>
+          <t>1613350</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2958382</t>
+          <t>2949616</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2662257</t>
+          <t>2865490</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3330640</t>
+          <t>3033907</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>510100</t>
+          <t>551409</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>383747</t>
+          <t>508398</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>564978</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>689381</t>
+          <t>763939</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>567094</t>
+          <t>722522</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>756029</t>
+          <t>804719</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1199481</t>
+          <t>1315348</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1044341</t>
+          <t>1253253</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1297988</t>
+          <t>1380159</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>143552</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>101090</t>
+          <t>123417</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>157080</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>225973</t>
+          <t>241598</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>185491</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>259761</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>358630</t>
+          <t>385151</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>310195</t>
+          <t>350008</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>400583</t>
+          <t>419181</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
